--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>7.9804</v>
       </c>
       <c r="N5" t="n">
-        <v>338.1111</v>
+        <v>338.2511</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>5.4083</v>
       </c>
       <c r="N10" t="n">
-        <v>333.5408</v>
+        <v>333.6808</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>7.1589</v>
       </c>
       <c r="N16" t="n">
-        <v>318.9873</v>
+        <v>319.1273</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1638,13 +1638,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
@@ -1653,7 +1653,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6.0208</v>
+        <v>4.657</v>
       </c>
       <c r="N23" t="n">
-        <v>312.152</v>
+        <v>312.2325</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1692,13 +1692,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="C24" t="n">
-        <v>10</v>
-      </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
         <v>33</v>
@@ -1707,7 +1707,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.657</v>
+        <v>6.0208</v>
       </c>
       <c r="N24" t="n">
-        <v>312.0925</v>
+        <v>312.152</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         <v>7.2284</v>
       </c>
       <c r="N29" t="n">
-        <v>300.831</v>
+        <v>300.971</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:04</t>
+          <t>2026-05-24 05:36:59</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
         <v>331.3857</v>
       </c>
       <c r="C2" t="n">
-        <v>293.5481</v>
+        <v>293.6498</v>
       </c>
     </row>
     <row r="3">
@@ -2436,10 +2436,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>336.2673</v>
+        <v>336.9959</v>
       </c>
       <c r="C3" t="n">
-        <v>302.0926</v>
+        <v>303.2313</v>
       </c>
     </row>
     <row r="4">
@@ -2447,10 +2447,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>339.1556</v>
+        <v>336.9959</v>
       </c>
       <c r="C4" t="n">
-        <v>305.834</v>
+        <v>306.2481</v>
       </c>
     </row>
     <row r="5">
@@ -2458,10 +2458,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>340.4965</v>
+        <v>341.7867</v>
       </c>
       <c r="C5" t="n">
-        <v>309.5338</v>
+        <v>311.5461</v>
       </c>
     </row>
     <row r="6">
@@ -2469,10 +2469,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>340.8198</v>
+        <v>344.5017</v>
       </c>
       <c r="C6" t="n">
-        <v>310.9815</v>
+        <v>311.4085</v>
       </c>
     </row>
     <row r="7">
@@ -2480,10 +2480,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>342.491</v>
+        <v>344.6726</v>
       </c>
       <c r="C7" t="n">
-        <v>316.2492</v>
+        <v>316.6965</v>
       </c>
     </row>
     <row r="8">
@@ -2491,10 +2491,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>343.8918</v>
+        <v>344.6726</v>
       </c>
       <c r="C8" t="n">
-        <v>318.2876</v>
+        <v>318.4515</v>
       </c>
     </row>
     <row r="9">
@@ -2502,10 +2502,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>343.8918</v>
+        <v>344.6726</v>
       </c>
       <c r="C9" t="n">
-        <v>323.2006</v>
+        <v>319.9014</v>
       </c>
     </row>
     <row r="10">
@@ -2513,10 +2513,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>343.8918</v>
+        <v>344.6726</v>
       </c>
       <c r="C10" t="n">
-        <v>321.1623</v>
+        <v>322.1165</v>
       </c>
     </row>
     <row r="11">
@@ -2524,10 +2524,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C11" t="n">
-        <v>336.2024</v>
+        <v>325.1507</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C12" t="n">
-        <v>333.7807</v>
+        <v>335.138</v>
       </c>
     </row>
     <row r="13">
@@ -2546,10 +2546,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C13" t="n">
-        <v>328.7366</v>
+        <v>332.4512</v>
       </c>
     </row>
     <row r="14">
@@ -2557,10 +2557,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C14" t="n">
-        <v>339.3209</v>
+        <v>331.8813</v>
       </c>
     </row>
     <row r="15">
@@ -2568,10 +2568,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C15" t="n">
-        <v>341.9094</v>
+        <v>325.9412</v>
       </c>
     </row>
     <row r="16">
@@ -2579,10 +2579,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C16" t="n">
-        <v>338.9403</v>
+        <v>339.3125</v>
       </c>
     </row>
     <row r="17">
@@ -2590,10 +2590,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C17" t="n">
-        <v>339.5942</v>
+        <v>340.5488</v>
       </c>
     </row>
     <row r="18">
@@ -2601,10 +2601,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>345.1311</v>
+        <v>345.6924</v>
       </c>
       <c r="C18" t="n">
-        <v>338.9293</v>
+        <v>339.4567</v>
       </c>
     </row>
     <row r="19">
@@ -2615,7 +2615,7 @@
         <v>345.6924</v>
       </c>
       <c r="C19" t="n">
-        <v>340.3583</v>
+        <v>340.629</v>
       </c>
     </row>
     <row r="20">
@@ -2626,7 +2626,7 @@
         <v>345.6924</v>
       </c>
       <c r="C20" t="n">
-        <v>339.1403</v>
+        <v>341.0455</v>
       </c>
     </row>
     <row r="21">
@@ -2637,7 +2637,7 @@
         <v>345.6924</v>
       </c>
       <c r="C21" t="n">
-        <v>335.4057</v>
+        <v>342.0478</v>
       </c>
     </row>
     <row r="22">
@@ -2648,7 +2648,7 @@
         <v>345.6924</v>
       </c>
       <c r="C22" t="n">
-        <v>340.0491</v>
+        <v>339.8253</v>
       </c>
     </row>
     <row r="23">
@@ -2659,7 +2659,7 @@
         <v>345.6924</v>
       </c>
       <c r="C23" t="n">
-        <v>340.915</v>
+        <v>340.8503</v>
       </c>
     </row>
     <row r="24">
@@ -2670,7 +2670,7 @@
         <v>345.6924</v>
       </c>
       <c r="C24" t="n">
-        <v>341.2407</v>
+        <v>341.3115</v>
       </c>
     </row>
     <row r="25">
@@ -2681,7 +2681,7 @@
         <v>345.6924</v>
       </c>
       <c r="C25" t="n">
-        <v>340.5916</v>
+        <v>340.6482</v>
       </c>
     </row>
     <row r="26">
@@ -2692,7 +2692,7 @@
         <v>345.6924</v>
       </c>
       <c r="C26" t="n">
-        <v>339.232</v>
+        <v>339.2354</v>
       </c>
     </row>
     <row r="27">
@@ -2703,7 +2703,7 @@
         <v>345.6924</v>
       </c>
       <c r="C27" t="n">
-        <v>340.0561</v>
+        <v>339.9253</v>
       </c>
     </row>
     <row r="28">
@@ -2714,7 +2714,7 @@
         <v>345.6924</v>
       </c>
       <c r="C28" t="n">
-        <v>342.3772</v>
+        <v>342.4566</v>
       </c>
     </row>
     <row r="29">
@@ -2725,7 +2725,7 @@
         <v>345.6924</v>
       </c>
       <c r="C29" t="n">
-        <v>341.6335</v>
+        <v>341.6927</v>
       </c>
     </row>
     <row r="30">
@@ -2736,7 +2736,7 @@
         <v>345.6924</v>
       </c>
       <c r="C30" t="n">
-        <v>341.1403</v>
+        <v>341.1442</v>
       </c>
     </row>
     <row r="31">
@@ -2747,7 +2747,7 @@
         <v>345.6924</v>
       </c>
       <c r="C31" t="n">
-        <v>340.9368</v>
+        <v>340.9402</v>
       </c>
     </row>
     <row r="32">
@@ -2758,7 +2758,7 @@
         <v>345.6924</v>
       </c>
       <c r="C32" t="n">
-        <v>340.6147</v>
+        <v>340.6181</v>
       </c>
     </row>
     <row r="33">
@@ -2769,7 +2769,7 @@
         <v>345.6924</v>
       </c>
       <c r="C33" t="n">
-        <v>341.0361</v>
+        <v>341.0383</v>
       </c>
     </row>
     <row r="34">
@@ -2780,7 +2780,7 @@
         <v>345.6924</v>
       </c>
       <c r="C34" t="n">
-        <v>339.5346</v>
+        <v>339.5379</v>
       </c>
     </row>
     <row r="35">
@@ -2791,7 +2791,7 @@
         <v>345.6924</v>
       </c>
       <c r="C35" t="n">
-        <v>342.1788</v>
+        <v>342.1816</v>
       </c>
     </row>
     <row r="36">
@@ -2802,7 +2802,7 @@
         <v>345.6924</v>
       </c>
       <c r="C36" t="n">
-        <v>341.6137</v>
+        <v>341.3973</v>
       </c>
     </row>
     <row r="37">
@@ -2813,7 +2813,7 @@
         <v>345.6924</v>
       </c>
       <c r="C37" t="n">
-        <v>341.1475</v>
+        <v>341.3712</v>
       </c>
     </row>
     <row r="38">
@@ -2824,7 +2824,7 @@
         <v>345.6924</v>
       </c>
       <c r="C38" t="n">
-        <v>340.3147</v>
+        <v>340.3203</v>
       </c>
     </row>
     <row r="39">
@@ -2835,7 +2835,7 @@
         <v>345.6924</v>
       </c>
       <c r="C39" t="n">
-        <v>340.2854</v>
+        <v>340.2871</v>
       </c>
     </row>
     <row r="40">
@@ -2846,7 +2846,7 @@
         <v>345.6924</v>
       </c>
       <c r="C40" t="n">
-        <v>341.1071</v>
+        <v>341.1029</v>
       </c>
     </row>
     <row r="41">
@@ -2857,7 +2857,7 @@
         <v>345.6924</v>
       </c>
       <c r="C41" t="n">
-        <v>340.0855</v>
+        <v>340.0942</v>
       </c>
     </row>
     <row r="42">
@@ -2868,7 +2868,7 @@
         <v>345.6924</v>
       </c>
       <c r="C42" t="n">
-        <v>340.9514</v>
+        <v>340.7766</v>
       </c>
     </row>
     <row r="43">
@@ -2879,7 +2879,7 @@
         <v>345.6924</v>
       </c>
       <c r="C43" t="n">
-        <v>340.0286</v>
+        <v>340.2106</v>
       </c>
     </row>
     <row r="44">
@@ -2890,7 +2890,7 @@
         <v>345.6924</v>
       </c>
       <c r="C44" t="n">
-        <v>340.4305</v>
+        <v>340.4355</v>
       </c>
     </row>
     <row r="45">
@@ -2901,7 +2901,7 @@
         <v>345.6924</v>
       </c>
       <c r="C45" t="n">
-        <v>342.2452</v>
+        <v>342.2491</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
         <v>345.6924</v>
       </c>
       <c r="C46" t="n">
-        <v>341.6595</v>
+        <v>341.215</v>
       </c>
     </row>
     <row r="47">
@@ -2923,7 +2923,7 @@
         <v>345.6924</v>
       </c>
       <c r="C47" t="n">
-        <v>341.1648</v>
+        <v>341.6144</v>
       </c>
     </row>
     <row r="48">
@@ -2934,7 +2934,7 @@
         <v>345.6924</v>
       </c>
       <c r="C48" t="n">
-        <v>341.1502</v>
+        <v>340.8686</v>
       </c>
     </row>
     <row r="49">
@@ -2945,7 +2945,7 @@
         <v>345.6924</v>
       </c>
       <c r="C49" t="n">
-        <v>341.5094</v>
+        <v>341.7989</v>
       </c>
     </row>
     <row r="50">
@@ -2956,7 +2956,7 @@
         <v>345.6924</v>
       </c>
       <c r="C50" t="n">
-        <v>340.7771</v>
+        <v>340.4164</v>
       </c>
     </row>
     <row r="51">
@@ -2967,7 +2967,7 @@
         <v>345.6924</v>
       </c>
       <c r="C51" t="n">
-        <v>339.1644</v>
+        <v>339.5307</v>
       </c>
     </row>
     <row r="52">
@@ -2978,7 +2978,7 @@
         <v>345.6924</v>
       </c>
       <c r="C52" t="n">
-        <v>342.2391</v>
+        <v>342.2413</v>
       </c>
     </row>
     <row r="53">
@@ -2989,7 +2989,7 @@
         <v>345.6924</v>
       </c>
       <c r="C53" t="n">
-        <v>340.6184</v>
+        <v>340.6201</v>
       </c>
     </row>
     <row r="54">
@@ -3000,7 +3000,7 @@
         <v>345.6924</v>
       </c>
       <c r="C54" t="n">
-        <v>340.7553</v>
+        <v>340.7614</v>
       </c>
     </row>
     <row r="55">
@@ -3011,7 +3011,7 @@
         <v>345.6924</v>
       </c>
       <c r="C55" t="n">
-        <v>340.9251</v>
+        <v>340.9296</v>
       </c>
     </row>
     <row r="56">
@@ -3022,7 +3022,7 @@
         <v>345.6924</v>
       </c>
       <c r="C56" t="n">
-        <v>340.2996</v>
+        <v>340.058</v>
       </c>
     </row>
     <row r="57">
@@ -3033,7 +3033,7 @@
         <v>345.6924</v>
       </c>
       <c r="C57" t="n">
-        <v>339.1691</v>
+        <v>339.4169</v>
       </c>
     </row>
     <row r="58">
@@ -3044,7 +3044,7 @@
         <v>345.6924</v>
       </c>
       <c r="C58" t="n">
-        <v>340.9702</v>
+        <v>340.9747</v>
       </c>
     </row>
     <row r="59">
@@ -3055,7 +3055,7 @@
         <v>345.6924</v>
       </c>
       <c r="C59" t="n">
-        <v>341.6609</v>
+        <v>341.6297</v>
       </c>
     </row>
     <row r="60">
@@ -3066,7 +3066,7 @@
         <v>345.6924</v>
       </c>
       <c r="C60" t="n">
-        <v>341.7296</v>
+        <v>341.6026</v>
       </c>
     </row>
     <row r="61">
@@ -3077,7 +3077,7 @@
         <v>345.6924</v>
       </c>
       <c r="C61" t="n">
-        <v>342.0681</v>
+        <v>342.2313</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
         <v>8.441000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -558,22 +558,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3" t="n">
         <v>35</v>
       </c>
-      <c r="F3" t="n">
-        <v>36</v>
-      </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -588,13 +588,13 @@
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9.496700000000001</v>
+        <v>7.9804</v>
       </c>
       <c r="N3" t="n">
-        <v>344.0018</v>
+        <v>345.7011</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -621,13 +621,13 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -645,10 +645,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>8.642200000000001</v>
+        <v>9.496700000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>340.0055</v>
+        <v>344.3318</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -666,43 +666,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>7.9804</v>
+        <v>8.642200000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>338.2511</v>
+        <v>340.3355</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -723,10 +723,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>33</v>
@@ -750,13 +750,13 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0208</v>
+        <v>10.2103</v>
       </c>
       <c r="N6" t="n">
-        <v>338.092</v>
+        <v>339.4257</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -774,13 +774,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>33</v>
@@ -789,13 +789,13 @@
         <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.3655</v>
+        <v>7.9804</v>
       </c>
       <c r="N7" t="n">
-        <v>337.6036</v>
+        <v>338.8211</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -831,19 +831,19 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" t="n">
         <v>33</v>
-      </c>
-      <c r="E8" t="n">
-        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -858,13 +858,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>10.8051</v>
+        <v>6.0208</v>
       </c>
       <c r="N8" t="n">
-        <v>336.9527</v>
+        <v>338.232</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -885,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
@@ -897,7 +897,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -906,19 +906,19 @@
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.5</v>
+        <v>7.3655</v>
       </c>
       <c r="N9" t="n">
-        <v>335.97</v>
+        <v>337.9336</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -939,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>33</v>
@@ -951,28 +951,28 @@
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4083</v>
+        <v>8.5</v>
       </c>
       <c r="N10" t="n">
-        <v>333.6808</v>
+        <v>336.11</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -993,10 +993,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
@@ -1005,7 +1005,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0311</v>
+        <v>5.4083</v>
       </c>
       <c r="N11" t="n">
-        <v>331.3078</v>
+        <v>333.8208</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1533</v>
+        <v>4.3875</v>
       </c>
       <c r="N12" t="n">
-        <v>331.2733</v>
+        <v>332.8487</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -1131,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6742</v>
+        <v>4.1533</v>
       </c>
       <c r="N13" t="n">
-        <v>330.7056</v>
+        <v>331.6033</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1158,37 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
         <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>8.775</v>
+        <v>3.6742</v>
       </c>
       <c r="N14" t="n">
-        <v>330.1574</v>
+        <v>331.0356</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1212,16 +1212,16 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="n">
-        <v>16</v>
-      </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1230,19 +1230,19 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>6.1033</v>
+        <v>8.775</v>
       </c>
       <c r="N15" t="n">
-        <v>324.9282</v>
+        <v>330.4874</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1263,40 +1263,40 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="n">
-        <v>30</v>
-      </c>
       <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="n">
         <v>33</v>
       </c>
-      <c r="F16" t="n">
-        <v>35</v>
-      </c>
       <c r="G16" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.1589</v>
+        <v>6.364</v>
       </c>
       <c r="N16" t="n">
-        <v>319.1273</v>
+        <v>328.3399</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1323,25 +1323,25 @@
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>6.1033</v>
       </c>
       <c r="N17" t="n">
-        <v>317.7582</v>
+        <v>325.2582</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1374,37 +1374,37 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="n">
         <v>33</v>
       </c>
-      <c r="F18" t="n">
-        <v>35</v>
-      </c>
       <c r="G18" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>9.0139</v>
+        <v>5.244</v>
       </c>
       <c r="N18" t="n">
-        <v>316.7947</v>
+        <v>323.7801</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1425,40 +1425,40 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F19" t="n">
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>9.604699999999999</v>
+        <v>7.1589</v>
       </c>
       <c r="N19" t="n">
-        <v>316.1917</v>
+        <v>319.2673</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>33</v>
@@ -1491,7 +1491,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.1589</v>
+        <v>9.0139</v>
       </c>
       <c r="N20" t="n">
-        <v>313.1273</v>
+        <v>316.9347</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1536,37 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="n">
-        <v>23</v>
-      </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6742</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>313.0356</v>
+        <v>316.5217</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1587,25 +1587,25 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="D22" t="n">
-        <v>32</v>
-      </c>
       <c r="E22" t="n">
+        <v>23</v>
+      </c>
+      <c r="F22" t="n">
         <v>33</v>
       </c>
-      <c r="F22" t="n">
-        <v>35</v>
-      </c>
       <c r="G22" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -1614,13 +1614,13 @@
         <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>8.381500000000001</v>
+        <v>3.6742</v>
       </c>
       <c r="N22" t="n">
-        <v>312.2838</v>
+        <v>313.6056</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1638,13 +1638,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
@@ -1653,28 +1653,28 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.657</v>
+        <v>7.1589</v>
       </c>
       <c r="N23" t="n">
-        <v>312.2325</v>
+        <v>313.2673</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1692,13 +1692,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
         <v>33</v>
@@ -1707,7 +1707,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6.0208</v>
+        <v>4.657</v>
       </c>
       <c r="N24" t="n">
-        <v>312.152</v>
+        <v>312.5625</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
@@ -1761,13 +1761,13 @@
         <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>3</v>
@@ -1776,13 +1776,13 @@
         <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>4.6098</v>
+        <v>8.381500000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>310.4344</v>
+        <v>312.4238</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1803,40 +1803,40 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>8.7464</v>
+        <v>6.0208</v>
       </c>
       <c r="N26" t="n">
-        <v>308.6961</v>
+        <v>312.292</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1857,10 +1857,10 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
         <v>33</v>
@@ -1869,28 +1869,28 @@
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.6789</v>
+        <v>4.6098</v>
       </c>
       <c r="N27" t="n">
-        <v>307.6873</v>
+        <v>310.5744</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1911,40 +1911,40 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="n">
-        <v>21</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>33</v>
       </c>
-      <c r="F28" t="n">
-        <v>35</v>
-      </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9051</v>
+        <v>8.7464</v>
       </c>
       <c r="N28" t="n">
-        <v>306.4928</v>
+        <v>309.0261</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -1968,37 +1968,37 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>7.2284</v>
+        <v>5.6789</v>
       </c>
       <c r="N29" t="n">
-        <v>300.971</v>
+        <v>308.0173</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2019,40 +2019,40 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3012</v>
+        <v>3.9051</v>
       </c>
       <c r="N30" t="n">
-        <v>298.8029</v>
+        <v>306.6328</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2073,25 +2073,25 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="D31" t="n">
-        <v>33</v>
-      </c>
       <c r="E31" t="n">
+        <v>31</v>
+      </c>
+      <c r="F31" t="n">
         <v>35</v>
       </c>
-      <c r="F31" t="n">
-        <v>36</v>
-      </c>
       <c r="G31" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -2100,13 +2100,13 @@
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>8.785600000000001</v>
+        <v>7.2284</v>
       </c>
       <c r="N31" t="n">
-        <v>295.2541</v>
+        <v>301.541</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E32" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2154,13 +2154,13 @@
         <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>4.0311</v>
+        <v>8.785600000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>293.4078</v>
+        <v>295.3941</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2181,40 +2181,40 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F33" t="n">
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>9.604699999999999</v>
+        <v>4.0311</v>
       </c>
       <c r="N33" t="n">
-        <v>290.4217</v>
+        <v>293.9778</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2235,19 +2235,19 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
         <v>6</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>10</v>
       </c>
-      <c r="E34" t="n">
-        <v>15</v>
-      </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2256,19 +2256,19 @@
         <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>5.7879</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>286.7298</v>
+        <v>290.7517</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2295,19 +2295,19 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2319,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5355</v>
+        <v>5.7879</v>
       </c>
       <c r="N35" t="n">
-        <v>273.2088</v>
+        <v>287.0598</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:59</t>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2352,10 +2352,10 @@
         <v>21</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -2373,19 +2373,73 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
+        <v>3.5355</v>
+      </c>
+      <c r="N36" t="n">
+        <v>273.5388</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35</v>
+      </c>
+      <c r="G37" t="n">
+        <v>73</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>4.1533</v>
       </c>
-      <c r="N36" t="n">
-        <v>234.1333</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>DailyLottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-05-24 05:36:59</t>
+      <c r="N37" t="n">
+        <v>234.4633</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:14</t>
         </is>
       </c>
     </row>
@@ -2425,10 +2479,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>331.3857</v>
+        <v>331.5257</v>
       </c>
       <c r="C2" t="n">
-        <v>293.6498</v>
+        <v>293.7597</v>
       </c>
     </row>
     <row r="3">
@@ -2436,10 +2490,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>336.9959</v>
+        <v>337.1359</v>
       </c>
       <c r="C3" t="n">
-        <v>303.2313</v>
+        <v>303.0369</v>
       </c>
     </row>
     <row r="4">
@@ -2447,10 +2501,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>336.9959</v>
+        <v>337.4151</v>
       </c>
       <c r="C4" t="n">
-        <v>306.2481</v>
+        <v>310.5097</v>
       </c>
     </row>
     <row r="5">
@@ -2458,10 +2512,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>341.7867</v>
+        <v>337.4151</v>
       </c>
       <c r="C5" t="n">
-        <v>311.5461</v>
+        <v>310.42</v>
       </c>
     </row>
     <row r="6">
@@ -2469,10 +2523,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>344.5017</v>
+        <v>343.4865</v>
       </c>
       <c r="C6" t="n">
-        <v>311.4085</v>
+        <v>313.3764</v>
       </c>
     </row>
     <row r="7">
@@ -2480,10 +2534,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>344.6726</v>
+        <v>343.4865</v>
       </c>
       <c r="C7" t="n">
-        <v>316.6965</v>
+        <v>316.315</v>
       </c>
     </row>
     <row r="8">
@@ -2491,10 +2545,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>344.6726</v>
+        <v>346.0224</v>
       </c>
       <c r="C8" t="n">
-        <v>318.4515</v>
+        <v>320.3538</v>
       </c>
     </row>
     <row r="9">
@@ -2502,10 +2556,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>344.6726</v>
+        <v>346.0224</v>
       </c>
       <c r="C9" t="n">
-        <v>319.9014</v>
+        <v>325.2422</v>
       </c>
     </row>
     <row r="10">
@@ -2513,10 +2567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>344.6726</v>
+        <v>346.0224</v>
       </c>
       <c r="C10" t="n">
-        <v>322.1165</v>
+        <v>331.2194</v>
       </c>
     </row>
     <row r="11">
@@ -2524,10 +2578,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C11" t="n">
-        <v>325.1507</v>
+        <v>330.8135</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2589,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C12" t="n">
-        <v>335.138</v>
+        <v>339.6329</v>
       </c>
     </row>
     <row r="13">
@@ -2546,10 +2600,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C13" t="n">
-        <v>332.4512</v>
+        <v>341.6689</v>
       </c>
     </row>
     <row r="14">
@@ -2557,10 +2611,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C14" t="n">
-        <v>331.8813</v>
+        <v>340.1465</v>
       </c>
     </row>
     <row r="15">
@@ -2568,10 +2622,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C15" t="n">
-        <v>325.9412</v>
+        <v>343.1065</v>
       </c>
     </row>
     <row r="16">
@@ -2579,10 +2633,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C16" t="n">
-        <v>339.3125</v>
+        <v>340.0951</v>
       </c>
     </row>
     <row r="17">
@@ -2590,10 +2644,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C17" t="n">
-        <v>340.5488</v>
+        <v>340.2858</v>
       </c>
     </row>
     <row r="18">
@@ -2601,10 +2655,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C18" t="n">
-        <v>339.4567</v>
+        <v>340.4028</v>
       </c>
     </row>
     <row r="19">
@@ -2612,10 +2666,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C19" t="n">
-        <v>340.629</v>
+        <v>340.6281</v>
       </c>
     </row>
     <row r="20">
@@ -2623,10 +2677,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C20" t="n">
-        <v>341.0455</v>
+        <v>341.1989</v>
       </c>
     </row>
     <row r="21">
@@ -2634,10 +2688,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C21" t="n">
-        <v>342.0478</v>
+        <v>342.4256</v>
       </c>
     </row>
     <row r="22">
@@ -2645,10 +2699,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C22" t="n">
-        <v>339.8253</v>
+        <v>340.8018</v>
       </c>
     </row>
     <row r="23">
@@ -2656,10 +2710,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C23" t="n">
-        <v>340.8503</v>
+        <v>340.6943</v>
       </c>
     </row>
     <row r="24">
@@ -2667,10 +2721,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C24" t="n">
-        <v>341.3115</v>
+        <v>341.2275</v>
       </c>
     </row>
     <row r="25">
@@ -2678,10 +2732,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C25" t="n">
-        <v>340.6482</v>
+        <v>341.0812</v>
       </c>
     </row>
     <row r="26">
@@ -2689,10 +2743,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C26" t="n">
-        <v>339.2354</v>
+        <v>339.1536</v>
       </c>
     </row>
     <row r="27">
@@ -2700,10 +2754,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C27" t="n">
-        <v>339.9253</v>
+        <v>340.8324</v>
       </c>
     </row>
     <row r="28">
@@ -2711,10 +2765,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C28" t="n">
-        <v>342.4566</v>
+        <v>342.2089</v>
       </c>
     </row>
     <row r="29">
@@ -2722,10 +2776,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C29" t="n">
-        <v>341.6927</v>
+        <v>342.8035</v>
       </c>
     </row>
     <row r="30">
@@ -2733,10 +2787,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C30" t="n">
-        <v>341.1442</v>
+        <v>340.9413</v>
       </c>
     </row>
     <row r="31">
@@ -2744,10 +2798,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C31" t="n">
-        <v>340.9402</v>
+        <v>341.4158</v>
       </c>
     </row>
     <row r="32">
@@ -2755,10 +2809,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C32" t="n">
-        <v>340.6181</v>
+        <v>340.7075</v>
       </c>
     </row>
     <row r="33">
@@ -2766,10 +2820,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C33" t="n">
-        <v>341.0383</v>
+        <v>341.447</v>
       </c>
     </row>
     <row r="34">
@@ -2777,10 +2831,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C34" t="n">
-        <v>339.5379</v>
+        <v>340.2228</v>
       </c>
     </row>
     <row r="35">
@@ -2788,10 +2842,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C35" t="n">
-        <v>342.1816</v>
+        <v>342.0948</v>
       </c>
     </row>
     <row r="36">
@@ -2799,10 +2853,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C36" t="n">
-        <v>341.3973</v>
+        <v>342.2655</v>
       </c>
     </row>
     <row r="37">
@@ -2810,10 +2864,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C37" t="n">
-        <v>341.3712</v>
+        <v>341.1657</v>
       </c>
     </row>
     <row r="38">
@@ -2821,10 +2875,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C38" t="n">
-        <v>340.3203</v>
+        <v>340.7647</v>
       </c>
     </row>
     <row r="39">
@@ -2832,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C39" t="n">
-        <v>340.2871</v>
+        <v>340.7968</v>
       </c>
     </row>
     <row r="40">
@@ -2843,10 +2897,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C40" t="n">
-        <v>341.1029</v>
+        <v>341.0547</v>
       </c>
     </row>
     <row r="41">
@@ -2854,10 +2908,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C41" t="n">
-        <v>340.0942</v>
+        <v>341.2728</v>
       </c>
     </row>
     <row r="42">
@@ -2865,10 +2919,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C42" t="n">
-        <v>340.7766</v>
+        <v>341.1631</v>
       </c>
     </row>
     <row r="43">
@@ -2876,10 +2930,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C43" t="n">
-        <v>340.2106</v>
+        <v>340.6239</v>
       </c>
     </row>
     <row r="44">
@@ -2887,10 +2941,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C44" t="n">
-        <v>340.4355</v>
+        <v>339.9737</v>
       </c>
     </row>
     <row r="45">
@@ -2898,10 +2952,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C45" t="n">
-        <v>342.2491</v>
+        <v>342.2217</v>
       </c>
     </row>
     <row r="46">
@@ -2909,10 +2963,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C46" t="n">
-        <v>341.215</v>
+        <v>342.8397</v>
       </c>
     </row>
     <row r="47">
@@ -2920,10 +2974,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C47" t="n">
-        <v>341.6144</v>
+        <v>341.3218</v>
       </c>
     </row>
     <row r="48">
@@ -2931,10 +2985,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C48" t="n">
-        <v>340.8686</v>
+        <v>340.5258</v>
       </c>
     </row>
     <row r="49">
@@ -2942,10 +2996,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C49" t="n">
-        <v>341.7989</v>
+        <v>342.831</v>
       </c>
     </row>
     <row r="50">
@@ -2953,10 +3007,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C50" t="n">
-        <v>340.4164</v>
+        <v>340.2868</v>
       </c>
     </row>
     <row r="51">
@@ -2964,10 +3018,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C51" t="n">
-        <v>339.5307</v>
+        <v>340.4355</v>
       </c>
     </row>
     <row r="52">
@@ -2975,10 +3029,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C52" t="n">
-        <v>342.2413</v>
+        <v>341.8409</v>
       </c>
     </row>
     <row r="53">
@@ -2986,10 +3040,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C53" t="n">
-        <v>340.6201</v>
+        <v>341.0019</v>
       </c>
     </row>
     <row r="54">
@@ -2997,10 +3051,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C54" t="n">
-        <v>340.7614</v>
+        <v>341.6961</v>
       </c>
     </row>
     <row r="55">
@@ -3008,10 +3062,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C55" t="n">
-        <v>340.9296</v>
+        <v>340.4594</v>
       </c>
     </row>
     <row r="56">
@@ -3019,10 +3073,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C56" t="n">
-        <v>340.058</v>
+        <v>341.9011</v>
       </c>
     </row>
     <row r="57">
@@ -3030,10 +3084,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C57" t="n">
-        <v>339.4169</v>
+        <v>339.161</v>
       </c>
     </row>
     <row r="58">
@@ -3041,10 +3095,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C58" t="n">
-        <v>340.9747</v>
+        <v>341.186</v>
       </c>
     </row>
     <row r="59">
@@ -3052,10 +3106,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C59" t="n">
-        <v>341.6297</v>
+        <v>341.6819</v>
       </c>
     </row>
     <row r="60">
@@ -3063,10 +3117,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C60" t="n">
-        <v>341.6026</v>
+        <v>341.945</v>
       </c>
     </row>
     <row r="61">
@@ -3074,10 +3128,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>345.6924</v>
+        <v>346.0224</v>
       </c>
       <c r="C61" t="n">
-        <v>342.2313</v>
+        <v>342.3352</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
         <v>8.441000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -615,40 +615,40 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9.496700000000001</v>
+        <v>6.0208</v>
       </c>
       <c r="N4" t="n">
-        <v>344.3318</v>
+        <v>338.372</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -672,37 +672,37 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>8.642200000000001</v>
+        <v>10.8051</v>
       </c>
       <c r="N5" t="n">
-        <v>340.3355</v>
+        <v>337.2327</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -723,11 +723,11 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>32</v>
-      </c>
       <c r="E6" t="n">
         <v>33</v>
       </c>
@@ -735,28 +735,28 @@
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>10.2103</v>
+        <v>10.7355</v>
       </c>
       <c r="N6" t="n">
-        <v>339.4257</v>
+        <v>336.9686</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>33</v>
@@ -789,7 +789,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -798,19 +798,19 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.9804</v>
+        <v>4.3229</v>
       </c>
       <c r="N7" t="n">
-        <v>338.8211</v>
+        <v>336.7373</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -828,13 +828,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
         <v>33</v>
@@ -843,7 +843,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -861,10 +861,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.0208</v>
+        <v>6.8328</v>
       </c>
       <c r="N8" t="n">
-        <v>338.232</v>
+        <v>335.7121</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -888,16 +888,16 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -906,19 +906,19 @@
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.3655</v>
+        <v>4.0311</v>
       </c>
       <c r="N9" t="n">
-        <v>337.9336</v>
+        <v>334.5978</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -939,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
         <v>33</v>
@@ -951,28 +951,28 @@
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8.5</v>
+        <v>5.4083</v>
       </c>
       <c r="N10" t="n">
-        <v>336.11</v>
+        <v>333.9608</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -990,13 +990,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
@@ -1005,28 +1005,28 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4083</v>
+        <v>4.9687</v>
       </c>
       <c r="N11" t="n">
-        <v>333.8208</v>
+        <v>333.6816</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1050,37 +1050,37 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3875</v>
+        <v>7.3655</v>
       </c>
       <c r="N12" t="n">
-        <v>332.8487</v>
+        <v>333.6636</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1533</v>
+        <v>3.9051</v>
       </c>
       <c r="N13" t="n">
-        <v>331.6033</v>
+        <v>332.7728</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1155,19 +1155,19 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -1176,19 +1176,19 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6742</v>
+        <v>6.0208</v>
       </c>
       <c r="N14" t="n">
-        <v>331.0356</v>
+        <v>332.452</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1212,37 +1212,37 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>8.775</v>
+        <v>4.1533</v>
       </c>
       <c r="N15" t="n">
-        <v>330.4874</v>
+        <v>331.7433</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1263,40 +1263,40 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6.364</v>
+        <v>4.0311</v>
       </c>
       <c r="N16" t="n">
-        <v>328.3399</v>
+        <v>331.5878</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1317,19 +1317,19 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
-        <v>16</v>
-      </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -1338,19 +1338,19 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.1033</v>
+        <v>8.6891</v>
       </c>
       <c r="N17" t="n">
-        <v>325.2582</v>
+        <v>331.5527</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1374,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="n">
-        <v>16</v>
-      </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1392,19 +1392,19 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.244</v>
+        <v>8.775</v>
       </c>
       <c r="N18" t="n">
-        <v>323.7801</v>
+        <v>330.6274</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1425,10 +1425,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>33</v>
@@ -1437,13 +1437,13 @@
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
@@ -1455,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7.1589</v>
+        <v>10.6888</v>
       </c>
       <c r="N19" t="n">
-        <v>319.2673</v>
+        <v>325.8819</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
         <v>33</v>
@@ -1491,19 +1491,19 @@
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>9.0139</v>
       </c>
       <c r="N20" t="n">
-        <v>316.9347</v>
+        <v>321.4247</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1536,37 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>9.604699999999999</v>
+        <v>6.1033</v>
       </c>
       <c r="N21" t="n">
-        <v>316.5217</v>
+        <v>318.2282</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1593,13 +1593,13 @@
         <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -1608,19 +1608,19 @@
         <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6742</v>
+        <v>4.717</v>
       </c>
       <c r="N22" t="n">
-        <v>313.6056</v>
+        <v>312.6325</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
@@ -1653,28 +1653,28 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>7.1589</v>
+        <v>8.381500000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>313.2673</v>
+        <v>312.5638</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1692,13 +1692,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
         <v>33</v>
@@ -1707,7 +1707,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
@@ -1716,19 +1716,19 @@
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.657</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>312.5625</v>
+        <v>311.97</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
@@ -1761,7 +1761,7 @@
         <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1770,19 +1770,19 @@
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8.381500000000001</v>
+        <v>6.5765</v>
       </c>
       <c r="N25" t="n">
-        <v>312.4238</v>
+        <v>311.9012</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1806,37 +1806,37 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
         <v>24</v>
       </c>
-      <c r="E26" t="n">
-        <v>33</v>
-      </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6.0208</v>
+        <v>3.937</v>
       </c>
       <c r="N26" t="n">
-        <v>312.292</v>
+        <v>311.8225</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1857,10 +1857,10 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
         <v>33</v>
@@ -1869,13 +1869,13 @@
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.6098</v>
+        <v>5.1235</v>
       </c>
       <c r="N27" t="n">
-        <v>310.5744</v>
+        <v>311.2487</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1911,40 +1911,40 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>8.7464</v>
+        <v>4.6098</v>
       </c>
       <c r="N28" t="n">
-        <v>309.0261</v>
+        <v>310.7144</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -1968,37 +1968,37 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.6789</v>
+        <v>6.9642</v>
       </c>
       <c r="N29" t="n">
-        <v>308.0173</v>
+        <v>308.2505</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2019,10 +2019,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
         <v>33</v>
@@ -2031,7 +2031,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H30" t="n">
         <v>3</v>
@@ -2049,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9051</v>
+        <v>5.6789</v>
       </c>
       <c r="N30" t="n">
-        <v>306.6328</v>
+        <v>308.1573</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2073,40 +2073,40 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F31" t="n">
         <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>7.2284</v>
+        <v>4.0311</v>
       </c>
       <c r="N31" t="n">
-        <v>301.541</v>
+        <v>307.1078</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="D32" t="n">
-        <v>33</v>
-      </c>
       <c r="E32" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G32" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2154,13 +2154,13 @@
         <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>8.785600000000001</v>
+        <v>3.937</v>
       </c>
       <c r="N32" t="n">
-        <v>295.3941</v>
+        <v>303.3225</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2178,22 +2178,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
@@ -2211,10 +2211,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.0311</v>
+        <v>6.2998</v>
       </c>
       <c r="N33" t="n">
-        <v>293.9778</v>
+        <v>302.0195</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2235,40 +2235,40 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>9.604699999999999</v>
+        <v>10.639</v>
       </c>
       <c r="N34" t="n">
-        <v>290.7517</v>
+        <v>297.6874</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2295,13 +2295,13 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -2310,19 +2310,19 @@
         <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5.7879</v>
+        <v>7.2284</v>
       </c>
       <c r="N35" t="n">
-        <v>287.0598</v>
+        <v>290.471</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2340,22 +2340,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F36" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5355</v>
+        <v>8.584099999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>273.5388</v>
+        <v>283.2604</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2406,10 +2406,10 @@
         <v>21</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1533</v>
+        <v>3.5355</v>
       </c>
       <c r="N37" t="n">
-        <v>234.4633</v>
+        <v>273.6788</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2439,7 +2439,61 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:14</t>
+          <t>2026-05-26 14:23:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33</v>
+      </c>
+      <c r="F38" t="n">
+        <v>35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>114</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7.3951</v>
+      </c>
+      <c r="N38" t="n">
+        <v>257.3177</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:33</t>
         </is>
       </c>
     </row>
@@ -2479,10 +2533,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>331.5257</v>
+        <v>331.6657</v>
       </c>
       <c r="C2" t="n">
-        <v>293.7597</v>
+        <v>293.8438</v>
       </c>
     </row>
     <row r="3">
@@ -2490,10 +2544,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>337.1359</v>
+        <v>337.2759</v>
       </c>
       <c r="C3" t="n">
-        <v>303.0369</v>
+        <v>301.9544</v>
       </c>
     </row>
     <row r="4">
@@ -2501,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>337.4151</v>
+        <v>338.386</v>
       </c>
       <c r="C4" t="n">
-        <v>310.5097</v>
+        <v>305.6075</v>
       </c>
     </row>
     <row r="5">
@@ -2512,10 +2566,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>337.4151</v>
+        <v>340.7081</v>
       </c>
       <c r="C5" t="n">
-        <v>310.42</v>
+        <v>313.6068</v>
       </c>
     </row>
     <row r="6">
@@ -2523,10 +2577,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>343.4865</v>
+        <v>340.7081</v>
       </c>
       <c r="C6" t="n">
-        <v>313.3764</v>
+        <v>311.2036</v>
       </c>
     </row>
     <row r="7">
@@ -2534,10 +2588,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>343.4865</v>
+        <v>344.6618</v>
       </c>
       <c r="C7" t="n">
-        <v>316.315</v>
+        <v>316.1114</v>
       </c>
     </row>
     <row r="8">
@@ -2545,10 +2599,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>346.0224</v>
+        <v>344.6618</v>
       </c>
       <c r="C8" t="n">
-        <v>320.3538</v>
+        <v>315.4599</v>
       </c>
     </row>
     <row r="9">
@@ -2556,10 +2610,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C9" t="n">
-        <v>325.2422</v>
+        <v>321.2266</v>
       </c>
     </row>
     <row r="10">
@@ -2567,10 +2621,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C10" t="n">
-        <v>331.2194</v>
+        <v>325.3405</v>
       </c>
     </row>
     <row r="11">
@@ -2578,10 +2632,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C11" t="n">
-        <v>330.8135</v>
+        <v>325.4896</v>
       </c>
     </row>
     <row r="12">
@@ -2589,10 +2643,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C12" t="n">
-        <v>339.6329</v>
+        <v>334.1932</v>
       </c>
     </row>
     <row r="13">
@@ -2600,10 +2654,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C13" t="n">
-        <v>341.6689</v>
+        <v>340.1781</v>
       </c>
     </row>
     <row r="14">
@@ -2611,10 +2665,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C14" t="n">
-        <v>340.1465</v>
+        <v>339.6264</v>
       </c>
     </row>
     <row r="15">
@@ -2622,10 +2676,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C15" t="n">
-        <v>343.1065</v>
+        <v>342.5831</v>
       </c>
     </row>
     <row r="16">
@@ -2633,10 +2687,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C16" t="n">
-        <v>340.0951</v>
+        <v>340.8933</v>
       </c>
     </row>
     <row r="17">
@@ -2644,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C17" t="n">
-        <v>340.2858</v>
+        <v>341.6842</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2709,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C18" t="n">
-        <v>340.4028</v>
+        <v>340.0605</v>
       </c>
     </row>
     <row r="19">
@@ -2666,10 +2720,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C19" t="n">
-        <v>340.6281</v>
+        <v>341.0871</v>
       </c>
     </row>
     <row r="20">
@@ -2677,10 +2731,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C20" t="n">
-        <v>341.1989</v>
+        <v>341.9004</v>
       </c>
     </row>
     <row r="21">
@@ -2688,10 +2742,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C21" t="n">
-        <v>342.4256</v>
+        <v>342.2369</v>
       </c>
     </row>
     <row r="22">
@@ -2699,10 +2753,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C22" t="n">
-        <v>340.8018</v>
+        <v>341.01</v>
       </c>
     </row>
     <row r="23">
@@ -2710,10 +2764,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C23" t="n">
-        <v>340.6943</v>
+        <v>340.2721</v>
       </c>
     </row>
     <row r="24">
@@ -2721,10 +2775,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C24" t="n">
-        <v>341.2275</v>
+        <v>340.5997</v>
       </c>
     </row>
     <row r="25">
@@ -2732,10 +2786,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C25" t="n">
-        <v>341.0812</v>
+        <v>340.8784</v>
       </c>
     </row>
     <row r="26">
@@ -2743,10 +2797,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C26" t="n">
-        <v>339.1536</v>
+        <v>340.2274</v>
       </c>
     </row>
     <row r="27">
@@ -2754,10 +2808,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C27" t="n">
-        <v>340.8324</v>
+        <v>340.9874</v>
       </c>
     </row>
     <row r="28">
@@ -2765,10 +2819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C28" t="n">
-        <v>342.2089</v>
+        <v>342.1071</v>
       </c>
     </row>
     <row r="29">
@@ -2776,10 +2830,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C29" t="n">
-        <v>342.8035</v>
+        <v>341.579</v>
       </c>
     </row>
     <row r="30">
@@ -2787,10 +2841,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C30" t="n">
-        <v>340.9413</v>
+        <v>340.9246</v>
       </c>
     </row>
     <row r="31">
@@ -2798,10 +2852,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C31" t="n">
-        <v>341.4158</v>
+        <v>341.5366</v>
       </c>
     </row>
     <row r="32">
@@ -2809,10 +2863,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C32" t="n">
-        <v>340.7075</v>
+        <v>339.9683</v>
       </c>
     </row>
     <row r="33">
@@ -2820,10 +2874,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C33" t="n">
-        <v>341.447</v>
+        <v>341.45</v>
       </c>
     </row>
     <row r="34">
@@ -2831,10 +2885,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C34" t="n">
-        <v>340.2228</v>
+        <v>340.5959</v>
       </c>
     </row>
     <row r="35">
@@ -2842,10 +2896,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C35" t="n">
-        <v>342.0948</v>
+        <v>342.5601</v>
       </c>
     </row>
     <row r="36">
@@ -2853,10 +2907,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C36" t="n">
-        <v>342.2655</v>
+        <v>341.6103</v>
       </c>
     </row>
     <row r="37">
@@ -2864,10 +2918,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C37" t="n">
-        <v>341.1657</v>
+        <v>341.6891</v>
       </c>
     </row>
     <row r="38">
@@ -2875,10 +2929,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C38" t="n">
-        <v>340.7647</v>
+        <v>341.1896</v>
       </c>
     </row>
     <row r="39">
@@ -2886,10 +2940,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C39" t="n">
-        <v>340.7968</v>
+        <v>341.3857</v>
       </c>
     </row>
     <row r="40">
@@ -2897,10 +2951,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C40" t="n">
-        <v>341.0547</v>
+        <v>342.4951</v>
       </c>
     </row>
     <row r="41">
@@ -2908,10 +2962,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C41" t="n">
-        <v>341.2728</v>
+        <v>341.2725</v>
       </c>
     </row>
     <row r="42">
@@ -2919,10 +2973,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C42" t="n">
-        <v>341.1631</v>
+        <v>339.9728</v>
       </c>
     </row>
     <row r="43">
@@ -2930,10 +2984,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C43" t="n">
-        <v>340.6239</v>
+        <v>339.5192</v>
       </c>
     </row>
     <row r="44">
@@ -2941,10 +2995,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C44" t="n">
-        <v>339.9737</v>
+        <v>342.6474</v>
       </c>
     </row>
     <row r="45">
@@ -2952,10 +3006,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C45" t="n">
-        <v>342.2217</v>
+        <v>340.4649</v>
       </c>
     </row>
     <row r="46">
@@ -2963,10 +3017,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C46" t="n">
-        <v>342.8397</v>
+        <v>342.3507</v>
       </c>
     </row>
     <row r="47">
@@ -2974,10 +3028,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C47" t="n">
-        <v>341.3218</v>
+        <v>340.8437</v>
       </c>
     </row>
     <row r="48">
@@ -2985,10 +3039,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C48" t="n">
-        <v>340.5258</v>
+        <v>341.5945</v>
       </c>
     </row>
     <row r="49">
@@ -2996,10 +3050,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C49" t="n">
-        <v>342.831</v>
+        <v>342.0199</v>
       </c>
     </row>
     <row r="50">
@@ -3007,10 +3061,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C50" t="n">
-        <v>340.2868</v>
+        <v>341.5381</v>
       </c>
     </row>
     <row r="51">
@@ -3018,10 +3072,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C51" t="n">
-        <v>340.4355</v>
+        <v>340.1069</v>
       </c>
     </row>
     <row r="52">
@@ -3029,10 +3083,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C52" t="n">
-        <v>341.8409</v>
+        <v>341.5865</v>
       </c>
     </row>
     <row r="53">
@@ -3040,10 +3094,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C53" t="n">
-        <v>341.0019</v>
+        <v>342.3721</v>
       </c>
     </row>
     <row r="54">
@@ -3051,10 +3105,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C54" t="n">
-        <v>341.6961</v>
+        <v>340.8256</v>
       </c>
     </row>
     <row r="55">
@@ -3062,10 +3116,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C55" t="n">
-        <v>340.4594</v>
+        <v>339.4705</v>
       </c>
     </row>
     <row r="56">
@@ -3073,10 +3127,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C56" t="n">
-        <v>341.9011</v>
+        <v>340.3763</v>
       </c>
     </row>
     <row r="57">
@@ -3084,10 +3138,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C57" t="n">
-        <v>339.161</v>
+        <v>338.6869</v>
       </c>
     </row>
     <row r="58">
@@ -3095,10 +3149,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C58" t="n">
-        <v>341.186</v>
+        <v>341.4822</v>
       </c>
     </row>
     <row r="59">
@@ -3106,10 +3160,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C59" t="n">
-        <v>341.6819</v>
+        <v>341.9337</v>
       </c>
     </row>
     <row r="60">
@@ -3117,10 +3171,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C60" t="n">
-        <v>341.945</v>
+        <v>341.7854</v>
       </c>
     </row>
     <row r="61">
@@ -3128,10 +3182,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>346.0224</v>
+        <v>346.1624</v>
       </c>
       <c r="C61" t="n">
-        <v>342.3352</v>
+        <v>341.6251</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>33</v>
@@ -627,13 +627,13 @@
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0208</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>338.372</v>
+        <v>344.9717</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -672,37 +672,37 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>10.8051</v>
+        <v>9.496700000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>337.2327</v>
+        <v>344.6618</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -720,13 +720,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>33</v>
@@ -735,7 +735,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -744,19 +744,19 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>10.7355</v>
+        <v>8.6891</v>
       </c>
       <c r="N6" t="n">
-        <v>336.9686</v>
+        <v>344.6427</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -774,28 +774,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -804,13 +804,13 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3229</v>
+        <v>8.642200000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>336.7373</v>
+        <v>340.4755</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -828,13 +828,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>33</v>
@@ -843,7 +843,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -858,13 +858,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8328</v>
+        <v>10.2103</v>
       </c>
       <c r="N8" t="n">
-        <v>335.7121</v>
+        <v>339.7057</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -882,43 +882,43 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0311</v>
+        <v>7.9804</v>
       </c>
       <c r="N9" t="n">
-        <v>334.5978</v>
+        <v>338.8211</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -939,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
         <v>33</v>
@@ -951,7 +951,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -969,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4083</v>
+        <v>6.0208</v>
       </c>
       <c r="N10" t="n">
-        <v>333.9608</v>
+        <v>338.372</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -990,13 +990,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
@@ -1005,7 +1005,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1014,19 +1014,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9687</v>
+        <v>7.3655</v>
       </c>
       <c r="N11" t="n">
-        <v>333.6816</v>
+        <v>338.0736</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -1059,13 +1059,13 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.3655</v>
+        <v>8.5</v>
       </c>
       <c r="N12" t="n">
-        <v>333.6636</v>
+        <v>336.44</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9051</v>
+        <v>4.3875</v>
       </c>
       <c r="N13" t="n">
-        <v>332.7728</v>
+        <v>333.1287</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1155,19 +1155,19 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -1176,19 +1176,19 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6.0208</v>
+        <v>4.1533</v>
       </c>
       <c r="N14" t="n">
-        <v>332.452</v>
+        <v>331.7433</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1215,13 +1215,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -1239,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1533</v>
+        <v>3.6742</v>
       </c>
       <c r="N15" t="n">
-        <v>331.7433</v>
+        <v>331.3156</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1263,25 +1263,25 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
         <v>33</v>
       </c>
-      <c r="F16" t="n">
-        <v>35</v>
-      </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -1290,13 +1290,13 @@
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.0311</v>
+        <v>8.775</v>
       </c>
       <c r="N16" t="n">
-        <v>331.5878</v>
+        <v>330.6274</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1317,19 +1317,19 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -1338,19 +1338,19 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8.6891</v>
+        <v>6.364</v>
       </c>
       <c r="N17" t="n">
-        <v>331.5527</v>
+        <v>328.4799</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1374,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1392,19 +1392,19 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>8.775</v>
+        <v>6.1033</v>
       </c>
       <c r="N18" t="n">
-        <v>330.6274</v>
+        <v>325.3982</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1425,40 +1425,40 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F19" t="n">
-        <v>35</v>
-      </c>
-      <c r="G19" t="n">
-        <v>79</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>10.6888</v>
+        <v>5.244</v>
       </c>
       <c r="N19" t="n">
-        <v>325.8819</v>
+        <v>323.9201</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1482,37 +1482,37 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
         <v>30</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>33</v>
       </c>
-      <c r="F20" t="n">
-        <v>35</v>
-      </c>
       <c r="G20" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>9.0139</v>
+        <v>6.9642</v>
       </c>
       <c r="N20" t="n">
-        <v>321.4247</v>
+        <v>320.3005</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.1033</v>
+        <v>7.1589</v>
       </c>
       <c r="N21" t="n">
-        <v>318.2282</v>
+        <v>319.4073</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1590,16 +1590,16 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
         <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -1608,19 +1608,19 @@
         <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.717</v>
+        <v>9.0139</v>
       </c>
       <c r="N22" t="n">
-        <v>312.6325</v>
+        <v>317.0747</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1641,40 +1641,40 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>8.381500000000001</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>312.5638</v>
+        <v>316.8517</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1695,40 +1695,40 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" t="n">
         <v>33</v>
       </c>
-      <c r="F24" t="n">
-        <v>35</v>
-      </c>
       <c r="G24" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>3.6742</v>
       </c>
       <c r="N24" t="n">
-        <v>311.97</v>
+        <v>313.8856</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
@@ -1761,13 +1761,13 @@
         <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5765</v>
+        <v>7.1589</v>
       </c>
       <c r="N25" t="n">
-        <v>311.9012</v>
+        <v>313.4073</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1803,40 +1803,40 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.937</v>
+        <v>8.381500000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>311.8225</v>
+        <v>312.7038</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1860,37 +1860,37 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1235</v>
+        <v>4.717</v>
       </c>
       <c r="N27" t="n">
-        <v>311.2487</v>
+        <v>312.6325</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>33</v>
@@ -1923,13 +1923,13 @@
         <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.6098</v>
+        <v>4.657</v>
       </c>
       <c r="N28" t="n">
-        <v>310.7144</v>
+        <v>312.5625</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -1968,22 +1968,22 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>6.9642</v>
+        <v>6.0208</v>
       </c>
       <c r="N29" t="n">
-        <v>308.2505</v>
+        <v>312.432</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2019,10 +2019,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>33</v>
@@ -2031,28 +2031,28 @@
         <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6789</v>
+        <v>4.6098</v>
       </c>
       <c r="N30" t="n">
-        <v>308.1573</v>
+        <v>310.7144</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2073,40 +2073,40 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
         <v>33</v>
       </c>
-      <c r="F31" t="n">
-        <v>35</v>
-      </c>
       <c r="G31" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>4.0311</v>
+        <v>8.7464</v>
       </c>
       <c r="N31" t="n">
-        <v>307.1078</v>
+        <v>309.1661</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2127,40 +2127,40 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.937</v>
+        <v>3.9051</v>
       </c>
       <c r="N32" t="n">
-        <v>303.3225</v>
+        <v>306.7728</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2178,13 +2178,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
         <v>33</v>
@@ -2193,28 +2193,28 @@
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>6.2998</v>
+        <v>4.272</v>
       </c>
       <c r="N33" t="n">
-        <v>302.0195</v>
+        <v>303.13</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -2247,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="G34" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
@@ -2265,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>10.639</v>
+        <v>8.785600000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>297.6874</v>
+        <v>295.7241</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2295,34 +2295,34 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F35" t="n">
         <v>35</v>
       </c>
       <c r="G35" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7.2284</v>
+        <v>4.0311</v>
       </c>
       <c r="N35" t="n">
-        <v>290.471</v>
+        <v>294.2578</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2340,43 +2340,43 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
         <v>6</v>
       </c>
-      <c r="C36" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" t="n">
-        <v>11</v>
-      </c>
       <c r="E36" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
         <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>8.584099999999999</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>283.2604</v>
+        <v>290.8917</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2403,19 +2403,19 @@
         <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5355</v>
+        <v>5.7879</v>
       </c>
       <c r="N37" t="n">
-        <v>273.6788</v>
+        <v>287.1998</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2448,43 +2448,43 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
         <v>6</v>
       </c>
-      <c r="C38" t="n">
-        <v>10</v>
-      </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>7.3951</v>
+        <v>4.1533</v>
       </c>
       <c r="N38" t="n">
-        <v>257.3177</v>
+        <v>234.6033</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:33</t>
+          <t>2026-05-27 14:58:24</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>331.6657</v>
       </c>
       <c r="C2" t="n">
-        <v>293.8438</v>
+        <v>293.9626</v>
       </c>
     </row>
     <row r="3">
@@ -2544,10 +2544,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>337.2759</v>
+        <v>337.4159</v>
       </c>
       <c r="C3" t="n">
-        <v>301.9544</v>
+        <v>302.8142</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>338.386</v>
+        <v>342.7834</v>
       </c>
       <c r="C4" t="n">
-        <v>305.6075</v>
+        <v>304.9803</v>
       </c>
     </row>
     <row r="5">
@@ -2566,10 +2566,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>340.7081</v>
+        <v>344.0447</v>
       </c>
       <c r="C5" t="n">
-        <v>313.6068</v>
+        <v>311.2064</v>
       </c>
     </row>
     <row r="6">
@@ -2577,10 +2577,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>340.7081</v>
+        <v>346.1624</v>
       </c>
       <c r="C6" t="n">
-        <v>311.2036</v>
+        <v>321.2337</v>
       </c>
     </row>
     <row r="7">
@@ -2588,10 +2588,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>344.6618</v>
+        <v>346.1624</v>
       </c>
       <c r="C7" t="n">
-        <v>316.1114</v>
+        <v>325.2432</v>
       </c>
     </row>
     <row r="8">
@@ -2599,10 +2599,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>344.6618</v>
+        <v>346.1624</v>
       </c>
       <c r="C8" t="n">
-        <v>315.4599</v>
+        <v>333.3813</v>
       </c>
     </row>
     <row r="9">
@@ -2613,7 +2613,7 @@
         <v>346.1624</v>
       </c>
       <c r="C9" t="n">
-        <v>321.2266</v>
+        <v>341.206</v>
       </c>
     </row>
     <row r="10">
@@ -2624,7 +2624,7 @@
         <v>346.1624</v>
       </c>
       <c r="C10" t="n">
-        <v>325.3405</v>
+        <v>340.6697</v>
       </c>
     </row>
     <row r="11">
@@ -2635,7 +2635,7 @@
         <v>346.1624</v>
       </c>
       <c r="C11" t="n">
-        <v>325.4896</v>
+        <v>341.4692</v>
       </c>
     </row>
     <row r="12">
@@ -2646,7 +2646,7 @@
         <v>346.1624</v>
       </c>
       <c r="C12" t="n">
-        <v>334.1932</v>
+        <v>340.9203</v>
       </c>
     </row>
     <row r="13">
@@ -2657,7 +2657,7 @@
         <v>346.1624</v>
       </c>
       <c r="C13" t="n">
-        <v>340.1781</v>
+        <v>341.0182</v>
       </c>
     </row>
     <row r="14">
@@ -2668,7 +2668,7 @@
         <v>346.1624</v>
       </c>
       <c r="C14" t="n">
-        <v>339.6264</v>
+        <v>341.4031</v>
       </c>
     </row>
     <row r="15">
@@ -2679,7 +2679,7 @@
         <v>346.1624</v>
       </c>
       <c r="C15" t="n">
-        <v>342.5831</v>
+        <v>342.2509</v>
       </c>
     </row>
     <row r="16">
@@ -2690,7 +2690,7 @@
         <v>346.1624</v>
       </c>
       <c r="C16" t="n">
-        <v>340.8933</v>
+        <v>341.214</v>
       </c>
     </row>
     <row r="17">
@@ -2701,7 +2701,7 @@
         <v>346.1624</v>
       </c>
       <c r="C17" t="n">
-        <v>341.6842</v>
+        <v>339.875</v>
       </c>
     </row>
     <row r="18">
@@ -2712,7 +2712,7 @@
         <v>346.1624</v>
       </c>
       <c r="C18" t="n">
-        <v>340.0605</v>
+        <v>340.5905</v>
       </c>
     </row>
     <row r="19">
@@ -2723,7 +2723,7 @@
         <v>346.1624</v>
       </c>
       <c r="C19" t="n">
-        <v>341.0871</v>
+        <v>340.5472</v>
       </c>
     </row>
     <row r="20">
@@ -2734,7 +2734,7 @@
         <v>346.1624</v>
       </c>
       <c r="C20" t="n">
-        <v>341.9004</v>
+        <v>341.0593</v>
       </c>
     </row>
     <row r="21">
@@ -2745,7 +2745,7 @@
         <v>346.1624</v>
       </c>
       <c r="C21" t="n">
-        <v>342.2369</v>
+        <v>342.0971</v>
       </c>
     </row>
     <row r="22">
@@ -2756,7 +2756,7 @@
         <v>346.1624</v>
       </c>
       <c r="C22" t="n">
-        <v>341.01</v>
+        <v>341.4661</v>
       </c>
     </row>
     <row r="23">
@@ -2767,7 +2767,7 @@
         <v>346.1624</v>
       </c>
       <c r="C23" t="n">
-        <v>340.2721</v>
+        <v>340.8755</v>
       </c>
     </row>
     <row r="24">
@@ -2778,7 +2778,7 @@
         <v>346.1624</v>
       </c>
       <c r="C24" t="n">
-        <v>340.5997</v>
+        <v>341.1986</v>
       </c>
     </row>
     <row r="25">
@@ -2789,7 +2789,7 @@
         <v>346.1624</v>
       </c>
       <c r="C25" t="n">
-        <v>340.8784</v>
+        <v>342.2082</v>
       </c>
     </row>
     <row r="26">
@@ -2800,7 +2800,7 @@
         <v>346.1624</v>
       </c>
       <c r="C26" t="n">
-        <v>340.2274</v>
+        <v>338.9698</v>
       </c>
     </row>
     <row r="27">
@@ -2811,7 +2811,7 @@
         <v>346.1624</v>
       </c>
       <c r="C27" t="n">
-        <v>340.9874</v>
+        <v>340.4155</v>
       </c>
     </row>
     <row r="28">
@@ -2822,7 +2822,7 @@
         <v>346.1624</v>
       </c>
       <c r="C28" t="n">
-        <v>342.1071</v>
+        <v>341.8976</v>
       </c>
     </row>
     <row r="29">
@@ -2833,7 +2833,7 @@
         <v>346.1624</v>
       </c>
       <c r="C29" t="n">
-        <v>341.579</v>
+        <v>343.0443</v>
       </c>
     </row>
     <row r="30">
@@ -2844,7 +2844,7 @@
         <v>346.1624</v>
       </c>
       <c r="C30" t="n">
-        <v>340.9246</v>
+        <v>341.6586</v>
       </c>
     </row>
     <row r="31">
@@ -2855,7 +2855,7 @@
         <v>346.1624</v>
       </c>
       <c r="C31" t="n">
-        <v>341.5366</v>
+        <v>341.7219</v>
       </c>
     </row>
     <row r="32">
@@ -2866,7 +2866,7 @@
         <v>346.1624</v>
       </c>
       <c r="C32" t="n">
-        <v>339.9683</v>
+        <v>340.8414</v>
       </c>
     </row>
     <row r="33">
@@ -2877,7 +2877,7 @@
         <v>346.1624</v>
       </c>
       <c r="C33" t="n">
-        <v>341.45</v>
+        <v>341.1216</v>
       </c>
     </row>
     <row r="34">
@@ -2888,7 +2888,7 @@
         <v>346.1624</v>
       </c>
       <c r="C34" t="n">
-        <v>340.5959</v>
+        <v>340.4892</v>
       </c>
     </row>
     <row r="35">
@@ -2899,7 +2899,7 @@
         <v>346.1624</v>
       </c>
       <c r="C35" t="n">
-        <v>342.5601</v>
+        <v>341.9297</v>
       </c>
     </row>
     <row r="36">
@@ -2910,7 +2910,7 @@
         <v>346.1624</v>
       </c>
       <c r="C36" t="n">
-        <v>341.6103</v>
+        <v>342.0514</v>
       </c>
     </row>
     <row r="37">
@@ -2921,7 +2921,7 @@
         <v>346.1624</v>
       </c>
       <c r="C37" t="n">
-        <v>341.6891</v>
+        <v>341.9212</v>
       </c>
     </row>
     <row r="38">
@@ -2932,7 +2932,7 @@
         <v>346.1624</v>
       </c>
       <c r="C38" t="n">
-        <v>341.1896</v>
+        <v>340.9578</v>
       </c>
     </row>
     <row r="39">
@@ -2943,7 +2943,7 @@
         <v>346.1624</v>
       </c>
       <c r="C39" t="n">
-        <v>341.3857</v>
+        <v>341.2827</v>
       </c>
     </row>
     <row r="40">
@@ -2954,7 +2954,7 @@
         <v>346.1624</v>
       </c>
       <c r="C40" t="n">
-        <v>342.4951</v>
+        <v>340.3114</v>
       </c>
     </row>
     <row r="41">
@@ -2965,7 +2965,7 @@
         <v>346.1624</v>
       </c>
       <c r="C41" t="n">
-        <v>341.2725</v>
+        <v>342.1374</v>
       </c>
     </row>
     <row r="42">
@@ -2976,7 +2976,7 @@
         <v>346.1624</v>
       </c>
       <c r="C42" t="n">
-        <v>339.9728</v>
+        <v>340.9045</v>
       </c>
     </row>
     <row r="43">
@@ -2987,7 +2987,7 @@
         <v>346.1624</v>
       </c>
       <c r="C43" t="n">
-        <v>339.5192</v>
+        <v>341.1589</v>
       </c>
     </row>
     <row r="44">
@@ -2998,7 +2998,7 @@
         <v>346.1624</v>
       </c>
       <c r="C44" t="n">
-        <v>342.6474</v>
+        <v>339.433</v>
       </c>
     </row>
     <row r="45">
@@ -3009,7 +3009,7 @@
         <v>346.1624</v>
       </c>
       <c r="C45" t="n">
-        <v>340.4649</v>
+        <v>342.6252</v>
       </c>
     </row>
     <row r="46">
@@ -3020,7 +3020,7 @@
         <v>346.1624</v>
       </c>
       <c r="C46" t="n">
-        <v>342.3507</v>
+        <v>343.0001</v>
       </c>
     </row>
     <row r="47">
@@ -3031,7 +3031,7 @@
         <v>346.1624</v>
       </c>
       <c r="C47" t="n">
-        <v>340.8437</v>
+        <v>341.178</v>
       </c>
     </row>
     <row r="48">
@@ -3042,7 +3042,7 @@
         <v>346.1624</v>
       </c>
       <c r="C48" t="n">
-        <v>341.5945</v>
+        <v>341.2239</v>
       </c>
     </row>
     <row r="49">
@@ -3053,7 +3053,7 @@
         <v>346.1624</v>
       </c>
       <c r="C49" t="n">
-        <v>342.0199</v>
+        <v>342.5079</v>
       </c>
     </row>
     <row r="50">
@@ -3064,7 +3064,7 @@
         <v>346.1624</v>
       </c>
       <c r="C50" t="n">
-        <v>341.5381</v>
+        <v>340.2624</v>
       </c>
     </row>
     <row r="51">
@@ -3075,7 +3075,7 @@
         <v>346.1624</v>
       </c>
       <c r="C51" t="n">
-        <v>340.1069</v>
+        <v>341.0486</v>
       </c>
     </row>
     <row r="52">
@@ -3086,7 +3086,7 @@
         <v>346.1624</v>
       </c>
       <c r="C52" t="n">
-        <v>341.5865</v>
+        <v>341.7443</v>
       </c>
     </row>
     <row r="53">
@@ -3097,7 +3097,7 @@
         <v>346.1624</v>
       </c>
       <c r="C53" t="n">
-        <v>342.3721</v>
+        <v>341.5379</v>
       </c>
     </row>
     <row r="54">
@@ -3108,7 +3108,7 @@
         <v>346.1624</v>
       </c>
       <c r="C54" t="n">
-        <v>340.8256</v>
+        <v>342.2683</v>
       </c>
     </row>
     <row r="55">
@@ -3119,7 +3119,7 @@
         <v>346.1624</v>
       </c>
       <c r="C55" t="n">
-        <v>339.4705</v>
+        <v>339.6556</v>
       </c>
     </row>
     <row r="56">
@@ -3130,7 +3130,7 @@
         <v>346.1624</v>
       </c>
       <c r="C56" t="n">
-        <v>340.3763</v>
+        <v>342.5835</v>
       </c>
     </row>
     <row r="57">
@@ -3141,7 +3141,7 @@
         <v>346.1624</v>
       </c>
       <c r="C57" t="n">
-        <v>338.6869</v>
+        <v>339.1067</v>
       </c>
     </row>
     <row r="58">
@@ -3152,7 +3152,7 @@
         <v>346.1624</v>
       </c>
       <c r="C58" t="n">
-        <v>341.4822</v>
+        <v>341.8581</v>
       </c>
     </row>
     <row r="59">
@@ -3163,7 +3163,7 @@
         <v>346.1624</v>
       </c>
       <c r="C59" t="n">
-        <v>341.9337</v>
+        <v>341.1155</v>
       </c>
     </row>
     <row r="60">
@@ -3174,7 +3174,7 @@
         <v>346.1624</v>
       </c>
       <c r="C60" t="n">
-        <v>341.7854</v>
+        <v>342.3182</v>
       </c>
     </row>
     <row r="61">
@@ -3185,7 +3185,7 @@
         <v>346.1624</v>
       </c>
       <c r="C61" t="n">
-        <v>341.6251</v>
+        <v>342.2887</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:24</t>
+          <t>2026-05-28 08:54:30</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
         <v>8.441000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
         <v>7.9804</v>
       </c>
       <c r="N3" t="n">
-        <v>345.7011</v>
+        <v>345.8411</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>9.496700000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>344.6618</v>
+        <v>344.8018</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
@@ -732,10 +732,10 @@
         <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -744,19 +744,19 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>8.6891</v>
+        <v>8.642200000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>344.6427</v>
+        <v>340.6155</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -780,37 +780,37 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>8.642200000000001</v>
+        <v>10.2103</v>
       </c>
       <c r="N7" t="n">
-        <v>340.4755</v>
+        <v>339.8457</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -828,13 +828,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>33</v>
@@ -843,7 +843,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -858,13 +858,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>10.2103</v>
+        <v>7.9804</v>
       </c>
       <c r="N8" t="n">
-        <v>339.7057</v>
+        <v>338.9611</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -882,13 +882,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
@@ -897,7 +897,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.9804</v>
+        <v>6.0208</v>
       </c>
       <c r="N9" t="n">
-        <v>338.8211</v>
+        <v>338.512</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -939,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>33</v>
@@ -951,13 +951,13 @@
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -969,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.0208</v>
+        <v>7.3655</v>
       </c>
       <c r="N10" t="n">
-        <v>338.372</v>
+        <v>338.0736</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -993,10 +993,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
@@ -1005,7 +1005,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1014,19 +1014,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.3655</v>
+        <v>8.5</v>
       </c>
       <c r="N11" t="n">
-        <v>338.0736</v>
+        <v>336.58</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -1059,28 +1059,28 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8.5</v>
+        <v>5.4083</v>
       </c>
       <c r="N12" t="n">
-        <v>336.44</v>
+        <v>334.1008</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>4.3875</v>
       </c>
       <c r="N13" t="n">
-        <v>333.1287</v>
+        <v>333.2687</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         <v>4.1533</v>
       </c>
       <c r="N14" t="n">
-        <v>331.7433</v>
+        <v>331.8833</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>3.6742</v>
       </c>
       <c r="N15" t="n">
-        <v>331.3156</v>
+        <v>331.4556</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>8.775</v>
       </c>
       <c r="N16" t="n">
-        <v>330.6274</v>
+        <v>330.7674</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>6.364</v>
       </c>
       <c r="N17" t="n">
-        <v>328.4799</v>
+        <v>328.6199</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>6.1033</v>
       </c>
       <c r="N18" t="n">
-        <v>325.3982</v>
+        <v>325.5382</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
         <v>5.244</v>
       </c>
       <c r="N19" t="n">
-        <v>323.9201</v>
+        <v>324.0601</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1479,40 +1479,40 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6.9642</v>
+        <v>7.1589</v>
       </c>
       <c r="N20" t="n">
-        <v>320.3005</v>
+        <v>319.5473</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>33</v>
@@ -1545,28 +1545,28 @@
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7.1589</v>
+        <v>9.0139</v>
       </c>
       <c r="N21" t="n">
-        <v>319.4073</v>
+        <v>317.0747</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1590,37 +1590,37 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F22" t="n">
         <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>9.0139</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>317.0747</v>
+        <v>316.9917</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1644,37 +1644,37 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.604699999999999</v>
+        <v>3.6742</v>
       </c>
       <c r="N23" t="n">
-        <v>316.8517</v>
+        <v>314.0256</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1695,19 +1695,19 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
@@ -1716,19 +1716,19 @@
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6742</v>
+        <v>7.1589</v>
       </c>
       <c r="N24" t="n">
-        <v>313.8856</v>
+        <v>313.5473</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
@@ -1761,28 +1761,28 @@
         <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>7.1589</v>
+        <v>8.381500000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>313.4073</v>
+        <v>313.0338</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1803,40 +1803,40 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="D26" t="n">
-        <v>32</v>
-      </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>8.381500000000001</v>
+        <v>4.717</v>
       </c>
       <c r="N26" t="n">
-        <v>312.7038</v>
+        <v>312.7725</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1854,43 +1854,43 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F27" t="n">
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.717</v>
+        <v>4.657</v>
       </c>
       <c r="N27" t="n">
-        <v>312.6325</v>
+        <v>312.7025</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="C28" t="n">
-        <v>10</v>
-      </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
         <v>33</v>
@@ -1923,7 +1923,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H28" t="n">
         <v>3</v>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.657</v>
+        <v>6.0208</v>
       </c>
       <c r="N28" t="n">
-        <v>312.5625</v>
+        <v>312.432</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -1965,10 +1965,10 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>33</v>
@@ -1977,13 +1977,13 @@
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>6.0208</v>
+        <v>4.6098</v>
       </c>
       <c r="N29" t="n">
-        <v>312.432</v>
+        <v>310.8544</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2019,40 +2019,40 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="n">
-        <v>18</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>33</v>
       </c>
-      <c r="F30" t="n">
-        <v>35</v>
-      </c>
       <c r="G30" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6098</v>
+        <v>8.7464</v>
       </c>
       <c r="N30" t="n">
-        <v>310.7144</v>
+        <v>309.3061</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2073,40 +2073,40 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
         <v>4</v>
       </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>8.7464</v>
+        <v>5.6789</v>
       </c>
       <c r="N31" t="n">
-        <v>309.1661</v>
+        <v>308.2973</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>3.9051</v>
       </c>
       <c r="N32" t="n">
-        <v>306.7728</v>
+        <v>306.9128</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
         <v>4.272</v>
       </c>
       <c r="N33" t="n">
-        <v>303.13</v>
+        <v>303.27</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2235,25 +2235,25 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="D34" t="n">
-        <v>33</v>
-      </c>
       <c r="E34" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34" t="n">
         <v>35</v>
       </c>
-      <c r="F34" t="n">
-        <v>36</v>
-      </c>
       <c r="G34" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -2262,13 +2262,13 @@
         <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>8.785600000000001</v>
+        <v>7.2284</v>
       </c>
       <c r="N34" t="n">
-        <v>295.7241</v>
+        <v>301.821</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2289,25 +2289,25 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2316,13 +2316,13 @@
         <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>4.0311</v>
+        <v>8.785600000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>294.2578</v>
+        <v>295.8641</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2343,40 +2343,40 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F36" t="n">
         <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>9.604699999999999</v>
+        <v>4.0311</v>
       </c>
       <c r="N36" t="n">
-        <v>290.8917</v>
+        <v>294.3978</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2397,19 +2397,19 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>10</v>
       </c>
-      <c r="E37" t="n">
-        <v>15</v>
-      </c>
       <c r="F37" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -2418,19 +2418,19 @@
         <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>5.7879</v>
+        <v>9.604699999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>287.1998</v>
+        <v>291.0317</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:30</t>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2457,19 +2457,19 @@
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G38" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
@@ -2481,19 +2481,127 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
+        <v>5.7879</v>
+      </c>
+      <c r="N38" t="n">
+        <v>287.5298</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="n">
+        <v>21</v>
+      </c>
+      <c r="F39" t="n">
+        <v>33</v>
+      </c>
+      <c r="G39" t="n">
+        <v>71</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.5355</v>
+      </c>
+      <c r="N39" t="n">
+        <v>273.8188</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>21</v>
+      </c>
+      <c r="F40" t="n">
+        <v>35</v>
+      </c>
+      <c r="G40" t="n">
+        <v>73</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>4.1533</v>
       </c>
-      <c r="N38" t="n">
-        <v>234.6033</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>DailyLottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:30</t>
+      <c r="N40" t="n">
+        <v>234.7433</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>DailyLottoGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:35</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2644,7 @@
         <v>331.6657</v>
       </c>
       <c r="C2" t="n">
-        <v>293.9626</v>
+        <v>294.0749</v>
       </c>
     </row>
     <row r="3">
@@ -2544,10 +2652,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>337.4159</v>
+        <v>335.155</v>
       </c>
       <c r="C3" t="n">
-        <v>302.8142</v>
+        <v>303.0874</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2663,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>342.7834</v>
+        <v>341.0565</v>
       </c>
       <c r="C4" t="n">
-        <v>304.9803</v>
+        <v>305.8087</v>
       </c>
     </row>
     <row r="5">
@@ -2566,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>344.0447</v>
+        <v>344.1847</v>
       </c>
       <c r="C5" t="n">
-        <v>311.2064</v>
+        <v>306.2525</v>
       </c>
     </row>
     <row r="6">
@@ -2577,10 +2685,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>346.1624</v>
+        <v>344.1847</v>
       </c>
       <c r="C6" t="n">
-        <v>321.2337</v>
+        <v>310.8475</v>
       </c>
     </row>
     <row r="7">
@@ -2588,10 +2696,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>346.1624</v>
+        <v>344.8018</v>
       </c>
       <c r="C7" t="n">
-        <v>325.2432</v>
+        <v>317.8676</v>
       </c>
     </row>
     <row r="8">
@@ -2599,10 +2707,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C8" t="n">
-        <v>333.3813</v>
+        <v>323.6606</v>
       </c>
     </row>
     <row r="9">
@@ -2610,10 +2718,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C9" t="n">
-        <v>341.206</v>
+        <v>333.4517</v>
       </c>
     </row>
     <row r="10">
@@ -2621,10 +2729,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C10" t="n">
-        <v>340.6697</v>
+        <v>334.717</v>
       </c>
     </row>
     <row r="11">
@@ -2632,10 +2740,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C11" t="n">
-        <v>341.4692</v>
+        <v>330.2777</v>
       </c>
     </row>
     <row r="12">
@@ -2643,10 +2751,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C12" t="n">
-        <v>340.9203</v>
+        <v>340.6679</v>
       </c>
     </row>
     <row r="13">
@@ -2654,10 +2762,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C13" t="n">
-        <v>341.0182</v>
+        <v>341.6505</v>
       </c>
     </row>
     <row r="14">
@@ -2665,10 +2773,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C14" t="n">
-        <v>341.4031</v>
+        <v>340.5497</v>
       </c>
     </row>
     <row r="15">
@@ -2676,10 +2784,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C15" t="n">
-        <v>342.2509</v>
+        <v>343.1656</v>
       </c>
     </row>
     <row r="16">
@@ -2687,10 +2795,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C16" t="n">
-        <v>341.214</v>
+        <v>340.7657</v>
       </c>
     </row>
     <row r="17">
@@ -2698,10 +2806,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C17" t="n">
-        <v>339.875</v>
+        <v>340.0191</v>
       </c>
     </row>
     <row r="18">
@@ -2709,10 +2817,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C18" t="n">
-        <v>340.5905</v>
+        <v>340.9448</v>
       </c>
     </row>
     <row r="19">
@@ -2720,10 +2828,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C19" t="n">
-        <v>340.5472</v>
+        <v>340.8983</v>
       </c>
     </row>
     <row r="20">
@@ -2731,10 +2839,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C20" t="n">
-        <v>341.0593</v>
+        <v>341.0838</v>
       </c>
     </row>
     <row r="21">
@@ -2742,10 +2850,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C21" t="n">
-        <v>342.0971</v>
+        <v>342.7</v>
       </c>
     </row>
     <row r="22">
@@ -2753,10 +2861,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C22" t="n">
-        <v>341.4661</v>
+        <v>341.3669</v>
       </c>
     </row>
     <row r="23">
@@ -2764,10 +2872,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C23" t="n">
-        <v>340.8755</v>
+        <v>340.8199</v>
       </c>
     </row>
     <row r="24">
@@ -2775,10 +2883,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C24" t="n">
-        <v>341.1986</v>
+        <v>341.4643</v>
       </c>
     </row>
     <row r="25">
@@ -2786,10 +2894,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C25" t="n">
-        <v>342.2082</v>
+        <v>341.5752</v>
       </c>
     </row>
     <row r="26">
@@ -2797,10 +2905,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C26" t="n">
-        <v>338.9698</v>
+        <v>339.5784</v>
       </c>
     </row>
     <row r="27">
@@ -2808,10 +2916,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C27" t="n">
-        <v>340.4155</v>
+        <v>340.7329</v>
       </c>
     </row>
     <row r="28">
@@ -2819,10 +2927,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C28" t="n">
-        <v>341.8976</v>
+        <v>342.6397</v>
       </c>
     </row>
     <row r="29">
@@ -2830,10 +2938,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C29" t="n">
-        <v>343.0443</v>
+        <v>342.9663</v>
       </c>
     </row>
     <row r="30">
@@ -2841,10 +2949,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C30" t="n">
-        <v>341.6586</v>
+        <v>341.3334</v>
       </c>
     </row>
     <row r="31">
@@ -2852,10 +2960,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C31" t="n">
-        <v>341.7219</v>
+        <v>341.8611</v>
       </c>
     </row>
     <row r="32">
@@ -2863,10 +2971,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C32" t="n">
-        <v>340.8414</v>
+        <v>341.0578</v>
       </c>
     </row>
     <row r="33">
@@ -2874,10 +2982,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C33" t="n">
-        <v>341.1216</v>
+        <v>341.8014</v>
       </c>
     </row>
     <row r="34">
@@ -2885,10 +2993,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C34" t="n">
-        <v>340.4892</v>
+        <v>339.9636</v>
       </c>
     </row>
     <row r="35">
@@ -2896,10 +3004,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C35" t="n">
-        <v>341.9297</v>
+        <v>342.5034</v>
       </c>
     </row>
     <row r="36">
@@ -2907,10 +3015,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C36" t="n">
-        <v>342.0514</v>
+        <v>342.4194</v>
       </c>
     </row>
     <row r="37">
@@ -2918,10 +3026,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C37" t="n">
-        <v>341.9212</v>
+        <v>341.5998</v>
       </c>
     </row>
     <row r="38">
@@ -2929,10 +3037,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C38" t="n">
-        <v>340.9578</v>
+        <v>341.298</v>
       </c>
     </row>
     <row r="39">
@@ -2940,10 +3048,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C39" t="n">
-        <v>341.2827</v>
+        <v>340.789</v>
       </c>
     </row>
     <row r="40">
@@ -2951,10 +3059,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C40" t="n">
-        <v>340.3114</v>
+        <v>341.4636</v>
       </c>
     </row>
     <row r="41">
@@ -2962,10 +3070,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C41" t="n">
-        <v>342.1374</v>
+        <v>341.5439</v>
       </c>
     </row>
     <row r="42">
@@ -2973,10 +3081,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C42" t="n">
-        <v>340.9045</v>
+        <v>341.3596</v>
       </c>
     </row>
     <row r="43">
@@ -2984,10 +3092,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C43" t="n">
-        <v>341.1589</v>
+        <v>341.2796</v>
       </c>
     </row>
     <row r="44">
@@ -2995,10 +3103,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C44" t="n">
-        <v>339.433</v>
+        <v>339.7342</v>
       </c>
     </row>
     <row r="45">
@@ -3006,10 +3114,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C45" t="n">
-        <v>342.6252</v>
+        <v>342.5071</v>
       </c>
     </row>
     <row r="46">
@@ -3017,10 +3125,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C46" t="n">
-        <v>343.0001</v>
+        <v>343.2498</v>
       </c>
     </row>
     <row r="47">
@@ -3028,10 +3136,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C47" t="n">
-        <v>341.178</v>
+        <v>341.5183</v>
       </c>
     </row>
     <row r="48">
@@ -3039,10 +3147,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C48" t="n">
-        <v>341.2239</v>
+        <v>340.9112</v>
       </c>
     </row>
     <row r="49">
@@ -3050,10 +3158,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C49" t="n">
-        <v>342.5079</v>
+        <v>343.0893</v>
       </c>
     </row>
     <row r="50">
@@ -3061,10 +3169,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C50" t="n">
-        <v>340.2624</v>
+        <v>340.7492</v>
       </c>
     </row>
     <row r="51">
@@ -3072,10 +3180,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C51" t="n">
-        <v>341.0486</v>
+        <v>340.5342</v>
       </c>
     </row>
     <row r="52">
@@ -3083,10 +3191,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C52" t="n">
-        <v>341.7443</v>
+        <v>342.272</v>
       </c>
     </row>
     <row r="53">
@@ -3094,10 +3202,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C53" t="n">
-        <v>341.5379</v>
+        <v>341.1563</v>
       </c>
     </row>
     <row r="54">
@@ -3105,10 +3213,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C54" t="n">
-        <v>342.2683</v>
+        <v>342.4214</v>
       </c>
     </row>
     <row r="55">
@@ -3116,10 +3224,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C55" t="n">
-        <v>339.6556</v>
+        <v>340.2912</v>
       </c>
     </row>
     <row r="56">
@@ -3127,10 +3235,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C56" t="n">
-        <v>342.5835</v>
+        <v>342.5019</v>
       </c>
     </row>
     <row r="57">
@@ -3138,10 +3246,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C57" t="n">
-        <v>339.1067</v>
+        <v>339.1203</v>
       </c>
     </row>
     <row r="58">
@@ -3149,10 +3257,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C58" t="n">
-        <v>341.8581</v>
+        <v>341.8996</v>
       </c>
     </row>
     <row r="59">
@@ -3160,10 +3268,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C59" t="n">
-        <v>341.1155</v>
+        <v>341.3891</v>
       </c>
     </row>
     <row r="60">
@@ -3171,10 +3279,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C60" t="n">
-        <v>342.3182</v>
+        <v>342.7669</v>
       </c>
     </row>
     <row r="61">
@@ -3182,10 +3290,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>346.1624</v>
+        <v>346.3024</v>
       </c>
       <c r="C61" t="n">
-        <v>342.2887</v>
+        <v>342.5007</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/daily_lotto_genetic_optimizer_results.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:35</t>
+          <t>2026-05-28 19:49:57</t>
         </is>
       </c>
     </row>
